--- a/光伏配储项目/电价数据/2026/鱼飞站.xlsx
+++ b/光伏配储项目/电价数据/2026/鱼飞站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.54053</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.10061</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.6313099999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.80913</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.6935399999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.5704900000000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44757</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.46299</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44037</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42538</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.46086</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41098</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40483</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40558</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40426</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41789</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39905</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42225</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39405</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42998</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41924</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42919</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41556</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.45301</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.53775</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.47059</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.43343</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.18471</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.25188</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.43523</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.45463</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.09745000000000001</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.12427</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.47033</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.41876</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.46736</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.46741</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.12045</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.26971</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.24494</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26316</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.27462</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.46592</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.72257</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.27927</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.1352</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.51797</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.55491</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.53903</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.66932</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.83954</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.41199</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.1036</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.93071</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.56238</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.7720399999999999</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.8261799999999999</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.8966799999999999</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.8706799999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.31425</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.6705099999999999</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.86464</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.47229</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.09506</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.92796</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.93951</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.29222</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.03672</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.02719</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.95452</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.63362</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47911</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40745</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41244</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42162</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.9015</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.66058</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.91932</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.05872</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53634</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52275</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5063</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.48785</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50119</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47533</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39209</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36276</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38335</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42443</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5597000000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.78423</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7267</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.46639</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.39758</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.64015</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.8517400000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.47959</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.87502</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.74038</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.5458</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.49395</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.44805</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.18882</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.7525299999999999</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.9579500000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.23225</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.65634</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.01445</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.9475</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.57904</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.01665</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.68863</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.9177999999999999</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.56102</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29218</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.52649</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.48142</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.47583</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5216000000000001</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.6733</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.75562</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.75566</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.7749299999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.6069199999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.27236</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.24301</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.15289</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.45051</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.24065</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.24322</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.8832000000000001</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.18606</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.73466</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.68643</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.9702799999999999</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.57459</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.30116</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.6788500000000001</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.78637</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.94213</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44049</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43454</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40836</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33333</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51761</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48657</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.54962</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.43976</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45043</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41961</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39408</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38633</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43633</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45369</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39512</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47576</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45143</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44646</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.52011</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.6640900000000001</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.86219</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.7044900000000001</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.47733</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.49804</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.29974</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.67443</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.3986</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.55767</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.8676900000000001</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.03847</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.46163</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.84104</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.6809500000000001</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.9464</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.7069500000000001</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.71438</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.58331</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.72945</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.7361</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.6552899999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.47917</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.4218</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.8433999999999999</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.72337</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.75164</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.41198</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.6154299999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.05986</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.7734500000000001</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.03475</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.14957</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.96323</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.14876</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.59302</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.2311</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.73712</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.7397</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.04972</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6881</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.21233</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.77332</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.79418</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.78025</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.79571</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.8169500000000001</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.83926</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.67022</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.5710299999999999</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.5312899999999999</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.43721</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.39342</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34316</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.7297100000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.47288</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.51901</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.43915</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.45277</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.62361</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.40059</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.6285599999999999</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47138</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39334</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.36678</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.40412</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.58777</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.73285</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.79039</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.87738</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.53264</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.0556</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.52944</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.70326</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.5252599999999999</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.8524700000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.28049</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.63634</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.58324</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.6712</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.59113</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.2136</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.48127</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.44905</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.57973</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.8483099999999999</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.9765499999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.03298</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.73782</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.60975</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.58775</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.82577</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.78972</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.6889700000000001</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.9054</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.50734</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.95043</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.85525</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.65101</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.5827</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.78864</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.8665700000000001</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.6995399999999999</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.83975</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.9132100000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.73819</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.85417</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.54147</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.9887999999999999</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.12299</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.19842</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.83266</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.69613</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.6840599999999999</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.66461</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.90366</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.48612</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.40404</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.47208</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31395</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.60888</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.42063</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.39182</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.37848</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.24835</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.24378</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.19237</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.22404</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.28176</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.48495</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.57636</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.41436</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.47474</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.22302</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.49233</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.21769</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.57392</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.47666</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.21855</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.39812</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.0338</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.20295</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.18623</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.13813</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.06492000000000001</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.07993</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.21795</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.21539</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.42968</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.41271</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.43397</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.37707</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.42853</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.42911</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.3988</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.42241</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40986</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37318</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40808</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34582</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.8646699999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.60922</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.6362599999999999</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.48499</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.47723</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.15562</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04425</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.19932</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04372</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04415</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04319</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04184</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01843</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.22132</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05725</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04345</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.1866</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.07648999999999999</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.01095</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04235</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.19725</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.1117</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.19797</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.06559999999999999</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.004160000000000001</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.10295</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.01252</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.01141</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.17175</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14597</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.25478</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.23509</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.29934</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.36495</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29747</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.30307</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33258</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.40124</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.19927</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30309</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28282</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.28388</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.21453</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.20428</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16013</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23742</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.25063</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.20763</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.29345</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.22299</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.29358</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.25737</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.38439</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.46548</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>-0.0111</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.43153</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.53006</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.1876</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.4391600000000001</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.52911</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.51575</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.57977</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.41155</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.4268</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.02227</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.21718</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.22468</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.54428</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.45839</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.44447</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.46508</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47969</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.58911</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.76854</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.68128</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.47391</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.58786</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.86421</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.09952</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.6230800000000001</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.10634</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.7873300000000001</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.53091</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.50893</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.07081</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.79601</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.41483</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.08192</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.5517</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.49255</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.18549</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.6221</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79571</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78762</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7813</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8785700000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87634</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49758</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41203</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40585</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45514</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21297</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6393</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53991</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50205</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.46076</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42938</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44318</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45323</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39515</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45576</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42338</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40208</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38441</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40526</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45338</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40211</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5960599999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4343399999999999</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.54362</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.48526</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.12409</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.46888</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.42496</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.64658</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.85388</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.29321</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.25093</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.31248</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.5357499999999999</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.83461</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.49888</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.54883</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.55525</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.56957</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5210399999999999</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.46167</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.41776</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.59065</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.5121100000000001</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.86211</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.26264</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.44697</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.44126</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.42402</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.41794</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.43198</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.36487</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.42834</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.40591</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.42543</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.39441</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.42166</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.43475</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.47644</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.42954</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.47883</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.43827</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.45794</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.44106</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.43421</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.42766</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.40403</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.44254</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41585</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45524</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41818</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35591</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9559</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47284</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.41187</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.44599</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.50536</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4128500000000001</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40219</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.5534600000000001</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.45187</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.54522</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.60096</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.90812</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.0805</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.5345700000000001</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.60165</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.5309199999999999</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.5620599999999999</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.49434</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.66303</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.18907</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.28336</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27567</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.52149</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.56411</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.56326</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.49104</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.49926</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.44787</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.30894</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.57956</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.17927</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.16786</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.36728</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.41426</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.40851</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39515</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.46555</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.39835</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.39548</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59674</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.10313</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.79785</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.39978</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70356</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79531</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64976</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58361</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.65359</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.39177</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.49312</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.06967</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.87181</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.8647100000000001</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.48336</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.29788</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.54637</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.2148</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.1647</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.61631</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.10748</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.35576</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.85275</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.09173</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.1664</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.11497</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.07903</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.69941</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.81636</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.3629</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.26228</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.14796</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.52615</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.80233</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.24458</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.68496</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.8612300000000001</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.7431599999999999</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.7414700000000001</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.85378</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.80214</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.05885</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.65547</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.6829700000000001</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.26736</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.5534</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.6263</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.66955</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.52108</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.5478</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.24431</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.52161</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.58778</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.7024400000000001</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.48303</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.47066</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.45309</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.6603300000000001</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.60597</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.78263</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.55745</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.5192599999999999</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.47346</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32488</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.43693</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39404</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.40208</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.3676</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.72151</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.42781</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.78685</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.26307</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.40069</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.37263</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.41116</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.41315</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.2896</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.5797100000000001</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39348</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40562</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45199</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40253</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39771</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45214</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43927</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44419</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40536</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39337</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.40046</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34933</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54299</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39495</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38465</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39497</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36303</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29293</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29144</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.47096</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.28287</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.26859</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26548</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29941</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30036</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30822</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.41063</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.29634</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30165</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.45023</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.62621</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.55232</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.65789</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.9022899999999999</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.36843</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.25183</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.90466</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.46086</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.40143</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.4356</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.7353500000000001</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.99949</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.24984</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.19678</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.09763</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.56043</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.44459</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.43719</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3823</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41953</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.42359</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41879</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.51534</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.44044</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.39011</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.63805</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.81287</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.80731</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.79604</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.79686</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.68663</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.4796</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.0126</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.15723</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.67144</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.08434</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.65528</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.53634</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.5291</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.59631</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.88442</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.40357</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.83012</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.46891</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.50901</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.98149</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.78892</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.5288</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.51182</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.54568</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.55908</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.55409</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.53091</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.55544</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.23265</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.58817</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.67038</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.71878</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.58582</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.59364</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.60185</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.53285</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.63616</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.09337</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.21369</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.57967</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.58818</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.58182</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.66164</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.61177</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.77368</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.68221</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.5723200000000001</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.42755</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.04252</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.73458</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.99441</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.54884</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.43495</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.33131</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.45093</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.8622300000000001</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.38157</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.60772</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.48842</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.44999</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.45297</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29822</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28336</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.42561</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.76681</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.30455</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.97685</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.79987</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.45917</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.42458</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50631</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.4429</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.41596</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.45302</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39324</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40304</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36967</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34927</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.38378</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.38251</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.2552</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.29079</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.26695</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.25318</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.18593</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.4069700000000001</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.60749</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.39045</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.45293</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.23961</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.44122</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.39537</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.40128</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5686</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.38426</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3877</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.41953</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37742</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40907</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37435</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65171</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83211</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47229</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40394</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.4594</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3448</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41354</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37369</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37951</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.44948</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.53498</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.43397</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.58547</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.80576</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.81796</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.23244</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.22572</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.42541</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.61156</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.52058</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.80645</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.81741</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.58829</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.5237999999999999</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.4679700000000001</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.08917</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.63226</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.55468</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.20361</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.20694</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.20385</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.19092</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.19697</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.08836</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.26178</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.20985</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.21159</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.18428</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.85766</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.24122</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.8912100000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.40103</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.98766</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.8201900000000001</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1.01101</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.7407899999999999</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.03041</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.30438</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.9685499999999999</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43269</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42166</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3766600000000001</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.68225</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5745800000000001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.60307</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.50959</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.4195</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.41956</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40772</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41633</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41391</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.4205</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40281</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.40028</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41605</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41384</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39663</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.4212</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.39182</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41876</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40159</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40155</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41467</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40064</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45165</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44967</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56236</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50171</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45182</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.50026</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.45118</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.37802</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.78334</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.48991</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.68573</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.18467</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.38595</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.48371</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.47345</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.48801</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.28937</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.26607</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.9134</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.99422</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.24768</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.38373</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.33274</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.17244</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.11672</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.63029</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.20576</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.96312</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.80889</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.23812</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.38585</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.7147</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.40104</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.42019</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.40706</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.39399</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.35584</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.98946</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.99068</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.9485399999999999</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.69902</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.6682100000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.95838</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.5328099999999999</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.16614</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.07323</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.14694</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.08244</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.93357</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.9847400000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.67865</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.8796900000000001</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.48286</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47575</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41966</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55302</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42972</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.45427</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45926</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.4372</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.4484</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41787</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39937</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40709</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37493</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36651</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.43514</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40021</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.47937</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.84524</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.63526</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.7313099999999999</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.19735</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.57994</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.5814400000000001</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39695</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.5407799999999999</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.47596</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.98222</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.5224800000000001</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.96229</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5331900000000001</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.59562</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.43796</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.22157</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.36685</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.43738</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.40763</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38838</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.5197200000000001</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46523</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36347</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41235</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40372</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.4059700000000001</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.3816000000000001</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38778</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4059700000000001</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40315</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38157</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39383</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36411</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.66923</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.91283</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.51402</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.40468</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.40424</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37691</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35605</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.38227</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.36664</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.23443</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.27498</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.23382</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.27382</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.28735</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.2361</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.29901</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26101</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.2781</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.40191</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28739</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.39453</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.41851</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.41401</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.42702</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.41562</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.42982</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.37646</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.37557</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.39545</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.42764</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.43634</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.36439</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.38284</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35221</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.63344</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30784</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.21056</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.27102</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.13721</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.28096</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.27558</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.23335</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.21691</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.21394</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.20825</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.2315</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.20986</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.17767</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.07636</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.00249</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.2053</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.2286</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.21329</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.2045</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.23688</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.4796</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.38645</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.20278</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.21266</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.2028</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.04203</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.20467</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.21409</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.26154</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.2609</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.36751</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.39032</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.68035</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.42138</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.3659</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.90518</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.9964500000000001</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.48522</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.53398</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.44005</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.6066699999999999</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.5845</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.44474</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.37671</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.36851</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.36622</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.45328</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.40671</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.66665</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.40236</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.6130099999999999</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.39617</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.98817</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.9917899999999999</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.68735</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.5301</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.6468200000000001</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11161</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.40313</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.36722</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.43549</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.53998</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.45203</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.38283</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.22669</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.5307000000000001</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.55022</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.21798</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.43921</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.5125700000000001</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.43191</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.54944</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.55064</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.67169</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.44849</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.6184400000000001</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.38514</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.68863</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.39669</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.38178</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.69039</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.84687</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.85194</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.27519</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.4639</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9418</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.84736</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.00717</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.19157</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8457100000000001</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8278799999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.47927</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.8469</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.8749</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.8476699999999999</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.38723</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.6353099999999999</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.37548</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33961</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.50062</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.6803899999999999</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.49089</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.63561</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.63675</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.49545</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.43041</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.42299</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.39749</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.30092</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.39641</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.38513</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.40298</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.47037</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.42022</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.49251</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.79452</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.6924400000000001</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.84436</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.7575</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.84684</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.26495</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.25982</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.7681399999999999</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.78687</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.5786399999999999</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.5860299999999999</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.15511</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.06262</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.47886</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.5740499999999999</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.43266</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.5629</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.27559</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.88009</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.4862</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.48048</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.44543</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.43489</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.44812</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.43749</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.45297</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.5048899999999999</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.49714</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.49588</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.44868</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.45982</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.36666</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.39674</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.45085</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.49244</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.56538</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.6987899999999999</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.58892</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.57855</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.50598</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.7152999999999999</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.5702999999999999</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.6839299999999999</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.39725</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.46029</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.45037</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.41922</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.48244</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34058</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.45478</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.43268</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.41874</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.41047</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.39458</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.39743</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.39463</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.36316</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38233</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.54367</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.45062</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.47563</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.68389</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.74033</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.45888</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.53727</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.43559</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.39657</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.40148</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.28959</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.39876</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.37776</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.37214</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.8286</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.91711</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.81047</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.11325</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.39546</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.39607</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.41428</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.20536</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.22771</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.27719</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.34494</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.32752</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.39639</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.4088</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.38748</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.92284</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.7994600000000001</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.73376</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.05901</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.06976</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.73461</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.83745</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.6264</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.5002</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.50149</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.62113</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.39515</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42448</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.69529</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45856</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.60837</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.29113</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36359</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36872</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47634</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40108</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37557</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.3786600000000001</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37734</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.3996499999999999</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.37547</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.36334</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.40115</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.42358</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.39672</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.643</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.40176</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.47924</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.18233</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.4868</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.46971</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.46994</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29277</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.49859</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.5145299999999999</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.44996</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.22787</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.02017</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.09493</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.23845</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.24367</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.34535</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.26417</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.34919</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.33096</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.36313</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.36951</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.29148</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.8606</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.8443999999999999</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.38721</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.46529</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.77547</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.75671</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.5795800000000001</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.79182</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.41474</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5730299999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.69468</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.41144</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.73529</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.71524</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.03926</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.98803</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.75598</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.75782</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39834</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.70594</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.49519</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.68277</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.40353</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37516</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27111</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37771</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.6396900000000001</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43402</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.46062</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38809</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.8629</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.41306</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.0727</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>1.00306</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>1.02916</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.00249</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.15365</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.9052</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.9329500000000001</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.73189</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.92091</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.12026</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.11176</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.26206</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.9589800000000001</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.23444</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.77249</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.21619</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.57435</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.40153</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.21134</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.39267</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.21071</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.18881</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.21011</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.55714</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.30328</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.44861</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.17152</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.40266</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.28027</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.6536900000000001</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.12353</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.57208</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.00881</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.13813</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.21418</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.1196</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.13021</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.21998</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.18917</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.22932</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.24786</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.6499400000000001</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.21845</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.69624</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.18907</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.1699</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.19832</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.25035</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.27183</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.25206</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.45638</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37577</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.25656</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.40612</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.39618</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.65892</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.13637</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.43989</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.53489</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.38278</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.38384</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37535</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37433</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.8675499999999999</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.37141</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.6673</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.46042</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.67257</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.87064</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.47497</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.37669</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.95773</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.51481</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.14214</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.67018</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.09161</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.13054</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.26701</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.27431</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.02949</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.15105</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.0022</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.69513</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.26876</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.00501</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.01441</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.02945</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.00921</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.05729</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.63748</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.09897</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.09465000000000001</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.01621</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37533</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.45146</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.41251</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.00385</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.07482999999999999</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.55972</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>-0.02496</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38707</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.43769</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.41705</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.28512</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.4702</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.47295</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.40135</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.38323</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.39169</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.38164</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.4196</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.37496</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39773</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3732799999999999</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.19438</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.36818</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19805</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.28555</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.41858</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.28398</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.56496</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.27113</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.4703</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.18952</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.36464</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.91353</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.58194</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.22393</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.85119</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.24383</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.28702</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.36433</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.24624</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.48377</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.87852</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.6905800000000001</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.42688</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.40414</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.6959099999999999</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.8575</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.49998</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.40751</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.40968</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.44164</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.40183</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.62013</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.14866</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.49571</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.40278</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40922</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40385</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.51393</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.19894</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.46279</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.46107</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.43152</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40861</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40975</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38404</v>
       </c>
     </row>
   </sheetData>
